--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/114.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/114.xlsx
@@ -426,13 +426,13 @@
         <v>-17.83764064663611</v>
       </c>
       <c r="E2">
-        <v>-25.32334071351536</v>
+        <v>-21.4547115818754</v>
       </c>
       <c r="F2">
-        <v>-4.208299563073848</v>
+        <v>-2.656815462939737</v>
       </c>
       <c r="G2">
-        <v>-18.47236458216643</v>
+        <v>-18.22907843132665</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.91925489106087</v>
       </c>
       <c r="E3">
-        <v>-26.38075247002804</v>
+        <v>-21.85297547544718</v>
       </c>
       <c r="F3">
-        <v>-4.211040630809712</v>
+        <v>-2.656117149219177</v>
       </c>
       <c r="G3">
-        <v>-18.03583764355392</v>
+        <v>-17.98097415134397</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.94600712318553</v>
       </c>
       <c r="E4">
-        <v>-26.16841538783485</v>
+        <v>-22.01453954919434</v>
       </c>
       <c r="F4">
-        <v>-4.13551506122687</v>
+        <v>-2.718392982194241</v>
       </c>
       <c r="G4">
-        <v>-18.0886373421646</v>
+        <v>-17.48862949337347</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.90780214882049</v>
       </c>
       <c r="E5">
-        <v>-26.21428760691758</v>
+        <v>-22.53241592892119</v>
       </c>
       <c r="F5">
-        <v>-2.954181136461898</v>
+        <v>-2.579778951214188</v>
       </c>
       <c r="G5">
-        <v>-17.80591589427605</v>
+        <v>-17.4143799172022</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.80073251628656</v>
       </c>
       <c r="E6">
-        <v>-25.83429784317505</v>
+        <v>-23.02247825240565</v>
       </c>
       <c r="F6">
-        <v>-3.491258940638777</v>
+        <v>-2.377683812687999</v>
       </c>
       <c r="G6">
-        <v>-17.693326228412</v>
+        <v>-17.10265440227868</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.63824952406424</v>
       </c>
       <c r="E7">
-        <v>-27.81878943161594</v>
+        <v>-24.26473698535247</v>
       </c>
       <c r="F7">
-        <v>-3.753300543003359</v>
+        <v>-2.570738977747438</v>
       </c>
       <c r="G7">
-        <v>-17.20083797948898</v>
+        <v>-16.80571222860235</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.44317739522827</v>
       </c>
       <c r="E8">
-        <v>-27.25274826015506</v>
+        <v>-24.18990027049038</v>
       </c>
       <c r="F8">
-        <v>-3.22062302647015</v>
+        <v>-2.328668485096949</v>
       </c>
       <c r="G8">
-        <v>-17.47715004940634</v>
+        <v>-16.33276409757152</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.22188442816647</v>
       </c>
       <c r="E9">
-        <v>-26.1200138630553</v>
+        <v>-25.08016603723533</v>
       </c>
       <c r="F9">
-        <v>-3.033935521636031</v>
+        <v>-2.133800023792782</v>
       </c>
       <c r="G9">
-        <v>-17.32871747105089</v>
+        <v>-16.14177768775322</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.00686046723984</v>
       </c>
       <c r="E10">
-        <v>-27.01650114036484</v>
+        <v>-25.62109273981497</v>
       </c>
       <c r="F10">
-        <v>-3.475316181604498</v>
+        <v>-2.388061599510271</v>
       </c>
       <c r="G10">
-        <v>-16.93422874184449</v>
+        <v>-15.40015783085091</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.79429126945158</v>
       </c>
       <c r="E11">
-        <v>-27.24929694154413</v>
+        <v>-25.62975633863856</v>
       </c>
       <c r="F11">
-        <v>-2.79926732009696</v>
+        <v>-2.271913720861544</v>
       </c>
       <c r="G11">
-        <v>-16.19398083122482</v>
+        <v>-15.46419025806485</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.61029998198397</v>
       </c>
       <c r="E12">
-        <v>-30.25630500494649</v>
+        <v>-25.66022014370618</v>
       </c>
       <c r="F12">
-        <v>-2.716235085109948</v>
+        <v>-2.059576647767141</v>
       </c>
       <c r="G12">
-        <v>-16.08241066112359</v>
+        <v>-15.11865037919724</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.44374800823411</v>
       </c>
       <c r="E13">
-        <v>-30.51099445962462</v>
+        <v>-26.85790661271494</v>
       </c>
       <c r="F13">
-        <v>-3.411367874843181</v>
+        <v>-2.230343759486856</v>
       </c>
       <c r="G13">
-        <v>-15.40273463576234</v>
+        <v>-14.47698157359341</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.30549163696924</v>
       </c>
       <c r="E14">
-        <v>-32.26594221135356</v>
+        <v>-28.27146247014864</v>
       </c>
       <c r="F14">
-        <v>-2.304302057943602</v>
+        <v>-1.617261589368317</v>
       </c>
       <c r="G14">
-        <v>-14.16150833480935</v>
+        <v>-13.91633853174709</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.18527617849113</v>
       </c>
       <c r="E15">
-        <v>-30.79888676223908</v>
+        <v>-28.69608264278779</v>
       </c>
       <c r="F15">
-        <v>-2.942548373024384</v>
+        <v>-1.689354404433958</v>
       </c>
       <c r="G15">
-        <v>-13.55783761135689</v>
+        <v>-13.54004016547927</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.06364965469923</v>
       </c>
       <c r="E16">
-        <v>-32.92392925172916</v>
+        <v>-29.29326459276223</v>
       </c>
       <c r="F16">
-        <v>-2.197585142175747</v>
+        <v>-1.531541302159221</v>
       </c>
       <c r="G16">
-        <v>-14.87866159877604</v>
+        <v>-13.48276303989483</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.93354963783946</v>
       </c>
       <c r="E17">
-        <v>-31.74442554190051</v>
+        <v>-30.03815550350421</v>
       </c>
       <c r="F17">
-        <v>-2.761755530628587</v>
+        <v>-1.443131305993236</v>
       </c>
       <c r="G17">
-        <v>-14.18654145932124</v>
+        <v>-13.32685589977503</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.76460992655085</v>
       </c>
       <c r="E18">
-        <v>-34.64634489915073</v>
+        <v>-30.8042672475104</v>
       </c>
       <c r="F18">
-        <v>-2.109291117446153</v>
+        <v>-1.017680979548007</v>
       </c>
       <c r="G18">
-        <v>-14.26010440966504</v>
+        <v>-12.6287819572802</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.5575926570263</v>
       </c>
       <c r="E19">
-        <v>-33.64606264101674</v>
+        <v>-31.09340966673363</v>
       </c>
       <c r="F19">
-        <v>-1.785758974404362</v>
+        <v>-1.310575954197259</v>
       </c>
       <c r="G19">
-        <v>-13.84716293768865</v>
+        <v>-12.22152407627867</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.28808078122449</v>
       </c>
       <c r="E20">
-        <v>-35.54570204548573</v>
+        <v>-32.32379852171409</v>
       </c>
       <c r="F20">
-        <v>-1.458804017254202</v>
+        <v>-0.7962028721637113</v>
       </c>
       <c r="G20">
-        <v>-13.4477542603003</v>
+        <v>-12.31868685235383</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.96333838460388</v>
       </c>
       <c r="E21">
-        <v>-35.33025836122157</v>
+        <v>-32.50794360543433</v>
       </c>
       <c r="F21">
-        <v>-1.892557070177691</v>
+        <v>-0.8420629483174976</v>
       </c>
       <c r="G21">
-        <v>-14.06927464452221</v>
+        <v>-12.09266816623968</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.57450732550736</v>
       </c>
       <c r="E22">
-        <v>-37.04615969668015</v>
+        <v>-33.36563988896998</v>
       </c>
       <c r="F22">
-        <v>-1.328940859517324</v>
+        <v>-0.4922790139135867</v>
       </c>
       <c r="G22">
-        <v>-12.95946539405209</v>
+        <v>-11.95169187443645</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.12599873177382</v>
       </c>
       <c r="E23">
-        <v>-36.15214773332021</v>
+        <v>-33.5096254957848</v>
       </c>
       <c r="F23">
-        <v>-1.600988311740321</v>
+        <v>-0.08464107173075563</v>
       </c>
       <c r="G23">
-        <v>-12.88859673212632</v>
+        <v>-11.90034374981843</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.63128816599355</v>
       </c>
       <c r="E24">
-        <v>-36.93290162385208</v>
+        <v>-33.45115035693687</v>
       </c>
       <c r="F24">
-        <v>-1.540187801109643</v>
+        <v>-0.4051157106888144</v>
       </c>
       <c r="G24">
-        <v>-12.84282646332722</v>
+        <v>-11.62871143958064</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.09833939553886</v>
       </c>
       <c r="E25">
-        <v>-38.36115777277001</v>
+        <v>-33.77219359234612</v>
       </c>
       <c r="F25">
-        <v>-2.199684225174441</v>
+        <v>-0.4567975529494755</v>
       </c>
       <c r="G25">
-        <v>-13.2944304519534</v>
+        <v>-11.43375147649467</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.56453757667518</v>
       </c>
       <c r="E26">
-        <v>-36.78824319680263</v>
+        <v>-34.20069286436265</v>
       </c>
       <c r="F26">
-        <v>-1.528381080517541</v>
+        <v>-0.4276166544510573</v>
       </c>
       <c r="G26">
-        <v>-13.03523442357538</v>
+        <v>-11.80520691154597</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.0449597218933</v>
       </c>
       <c r="E27">
-        <v>-36.52460564832516</v>
+        <v>-34.11597358315314</v>
       </c>
       <c r="F27">
-        <v>-1.480956218339867</v>
+        <v>-0.3609579295477811</v>
       </c>
       <c r="G27">
-        <v>-13.91706431874342</v>
+        <v>-11.59362564302067</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.58182839721146</v>
       </c>
       <c r="E28">
-        <v>-37.50339088464185</v>
+        <v>-33.38553792442723</v>
       </c>
       <c r="F28">
-        <v>-1.447066879523936</v>
+        <v>-0.3429964391528794</v>
       </c>
       <c r="G28">
-        <v>-12.71777571352978</v>
+        <v>-11.76242986142058</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.18991539460428</v>
       </c>
       <c r="E29">
-        <v>-35.82426623546463</v>
+        <v>-33.66609357923639</v>
       </c>
       <c r="F29">
-        <v>-1.616606350752702</v>
+        <v>-0.4470642359665813</v>
       </c>
       <c r="G29">
-        <v>-13.66647722065459</v>
+        <v>-11.70106430980646</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.8959333078363</v>
       </c>
       <c r="E30">
-        <v>-35.98379731226828</v>
+        <v>-33.54228842624891</v>
       </c>
       <c r="F30">
-        <v>-1.691028534955016</v>
+        <v>-0.4660686409216076</v>
       </c>
       <c r="G30">
-        <v>-13.55455590540586</v>
+        <v>-11.65889164705391</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.71361357989681</v>
       </c>
       <c r="E31">
-        <v>-36.13243659237257</v>
+        <v>-33.09325775404808</v>
       </c>
       <c r="F31">
-        <v>-2.545829141577853</v>
+        <v>-0.6035917120321731</v>
       </c>
       <c r="G31">
-        <v>-14.04423238240425</v>
+        <v>-11.94169011190789</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.63871932553563</v>
       </c>
       <c r="E32">
-        <v>-36.99998636977637</v>
+        <v>-33.25663055132721</v>
       </c>
       <c r="F32">
-        <v>-1.587528998179634</v>
+        <v>-0.6262202243744472</v>
       </c>
       <c r="G32">
-        <v>-13.58889111289588</v>
+        <v>-11.8485309126632</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.68032181502882</v>
       </c>
       <c r="E33">
-        <v>-37.17046531163226</v>
+        <v>-33.28345821987993</v>
       </c>
       <c r="F33">
-        <v>-1.47680278418223</v>
+        <v>-0.560958126912291</v>
       </c>
       <c r="G33">
-        <v>-14.37185211039846</v>
+        <v>-11.97136252955819</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.81487705726076</v>
       </c>
       <c r="E34">
-        <v>-35.63676951020524</v>
+        <v>-32.21837548205031</v>
       </c>
       <c r="F34">
-        <v>-1.705100840393774</v>
+        <v>-0.3657740576276575</v>
       </c>
       <c r="G34">
-        <v>-13.40346819980125</v>
+        <v>-11.80346293415911</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.04080337128051</v>
       </c>
       <c r="E35">
-        <v>-35.5218522294529</v>
+        <v>-32.47193526324807</v>
       </c>
       <c r="F35">
-        <v>-1.793667397998888</v>
+        <v>-0.7774461490621222</v>
       </c>
       <c r="G35">
-        <v>-12.91402538444376</v>
+        <v>-11.96352246355108</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.32722190527191</v>
       </c>
       <c r="E36">
-        <v>-35.56024451493961</v>
+        <v>-31.6571644953602</v>
       </c>
       <c r="F36">
-        <v>-1.616656881164273</v>
+        <v>-0.3111026374102929</v>
       </c>
       <c r="G36">
-        <v>-12.91816733073756</v>
+        <v>-12.27438251664264</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.66417486164898</v>
       </c>
       <c r="E37">
-        <v>-35.2994000010781</v>
+        <v>-31.86104356269037</v>
       </c>
       <c r="F37">
-        <v>-0.972376737921499</v>
+        <v>-0.540997785974434</v>
       </c>
       <c r="G37">
-        <v>-14.09646946555554</v>
+        <v>-11.6730262182702</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.0318600655002</v>
       </c>
       <c r="E38">
-        <v>-33.29068273097947</v>
+        <v>-31.70270238093128</v>
       </c>
       <c r="F38">
-        <v>-0.973632542904143</v>
+        <v>-0.525471695743763</v>
       </c>
       <c r="G38">
-        <v>-12.46673695662669</v>
+        <v>-12.30507965154495</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.41010831051089</v>
       </c>
       <c r="E39">
-        <v>-34.24297255564941</v>
+        <v>-30.88186792450916</v>
       </c>
       <c r="F39">
-        <v>-1.63966478577703</v>
+        <v>-0.2056017649897478</v>
       </c>
       <c r="G39">
-        <v>-14.52123499978508</v>
+        <v>-12.35402850188373</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.79880006107999</v>
       </c>
       <c r="E40">
-        <v>-31.75323034990914</v>
+        <v>-30.17821840222273</v>
       </c>
       <c r="F40">
-        <v>-0.5308196356962366</v>
+        <v>-0.2336527703507475</v>
       </c>
       <c r="G40">
-        <v>-14.24074704389423</v>
+        <v>-12.17668584329859</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.18016644008714</v>
       </c>
       <c r="E41">
-        <v>-33.62167498411735</v>
+        <v>-29.89603053536291</v>
       </c>
       <c r="F41">
-        <v>-1.276563188638311</v>
+        <v>0.09564563818193156</v>
       </c>
       <c r="G41">
-        <v>-14.51664139467702</v>
+        <v>-12.32611180997096</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.56629821087303</v>
       </c>
       <c r="E42">
-        <v>-33.21837947502553</v>
+        <v>-29.62108379244794</v>
       </c>
       <c r="F42">
-        <v>-1.577963839779508</v>
+        <v>-0.3788332697327916</v>
       </c>
       <c r="G42">
-        <v>-13.49116963747822</v>
+        <v>-12.69946917245689</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.9434349475463</v>
       </c>
       <c r="E43">
-        <v>-30.68323020987092</v>
+        <v>-28.39538806626454</v>
       </c>
       <c r="F43">
-        <v>-1.44797642693221</v>
+        <v>-0.2144023402770898</v>
       </c>
       <c r="G43">
-        <v>-13.81443464349446</v>
+        <v>-12.3192246657396</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.31886700265945</v>
       </c>
       <c r="E44">
-        <v>-31.62374152722364</v>
+        <v>-28.82950663320357</v>
       </c>
       <c r="F44">
-        <v>-1.621173140244336</v>
+        <v>-0.2316439793989587</v>
       </c>
       <c r="G44">
-        <v>-14.40964263835483</v>
+        <v>-12.63351784796848</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.68264832579114</v>
       </c>
       <c r="E45">
-        <v>-31.42645568287163</v>
+        <v>-27.89266260145067</v>
       </c>
       <c r="F45">
-        <v>-0.550133021692507</v>
+        <v>-0.2084944239603237</v>
       </c>
       <c r="G45">
-        <v>-14.49169573010893</v>
+        <v>-12.79999458756541</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-15.02932613133926</v>
       </c>
       <c r="E46">
-        <v>-29.572549364906</v>
+        <v>-27.6782032282705</v>
       </c>
       <c r="F46">
-        <v>-1.37940500169587</v>
+        <v>-0.03746968997833779</v>
       </c>
       <c r="G46">
-        <v>-14.09876169930654</v>
+        <v>-12.78868353662441</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-15.36040848806785</v>
       </c>
       <c r="E47">
-        <v>-31.03495114073101</v>
+        <v>-26.9818010597459</v>
       </c>
       <c r="F47">
-        <v>-1.199418160782996</v>
+        <v>0.08103158046174269</v>
       </c>
       <c r="G47">
-        <v>-14.6006669039697</v>
+        <v>-13.4630310322752</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-15.65881037539885</v>
       </c>
       <c r="E48">
-        <v>-29.95723018083993</v>
+        <v>-26.71690924144833</v>
       </c>
       <c r="F48">
-        <v>-1.107138032111131</v>
+        <v>-0.04631996730984771</v>
       </c>
       <c r="G48">
-        <v>-15.72878008476812</v>
+        <v>-12.93232409328287</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.93516238794874</v>
       </c>
       <c r="E49">
-        <v>-30.13329519192772</v>
+        <v>-26.20742650180897</v>
       </c>
       <c r="F49">
-        <v>-0.986845831346198</v>
+        <v>-0.1865228069684696</v>
       </c>
       <c r="G49">
-        <v>-14.6322190577256</v>
+        <v>-13.56090262550686</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-16.17145494153248</v>
       </c>
       <c r="E50">
-        <v>-28.89025980846316</v>
+        <v>-25.38212941981831</v>
       </c>
       <c r="F50">
-        <v>-1.275068813843661</v>
+        <v>0.03860011698814361</v>
       </c>
       <c r="G50">
-        <v>-14.64509002855979</v>
+        <v>-13.25389342068718</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-16.37961175686018</v>
       </c>
       <c r="E51">
-        <v>-28.48909282017532</v>
+        <v>-25.32401768696131</v>
       </c>
       <c r="F51">
-        <v>-0.7409747890516655</v>
+        <v>0.05117059232562611</v>
       </c>
       <c r="G51">
-        <v>-14.87279917179669</v>
+        <v>-13.17945717627766</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-16.54754747362375</v>
       </c>
       <c r="E52">
-        <v>-27.80854761248892</v>
+        <v>-24.67132806763053</v>
       </c>
       <c r="F52">
-        <v>-1.440699219298616</v>
+        <v>-0.06841252594251052</v>
       </c>
       <c r="G52">
-        <v>-14.94351902128077</v>
+        <v>-13.41462260606678</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-16.6821759244407</v>
       </c>
       <c r="E53">
-        <v>-27.90620622358094</v>
+        <v>-23.81177114542137</v>
       </c>
       <c r="F53">
-        <v>-1.161592420068962</v>
+        <v>-0.022028921590155</v>
       </c>
       <c r="G53">
-        <v>-15.23334169445714</v>
+        <v>-13.53236979787058</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-16.7861308755546</v>
       </c>
       <c r="E54">
-        <v>-25.3811907940589</v>
+        <v>-23.87182658117839</v>
       </c>
       <c r="F54">
-        <v>-1.043765440694761</v>
+        <v>-0.1145004031320666</v>
       </c>
       <c r="G54">
-        <v>-16.09244505795954</v>
+        <v>-13.40184301129328</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-16.85220555281851</v>
       </c>
       <c r="E55">
-        <v>-27.82374836593779</v>
+        <v>-23.2096510271817</v>
       </c>
       <c r="F55">
-        <v>-1.121147381627276</v>
+        <v>-0.2891856926670235</v>
       </c>
       <c r="G55">
-        <v>-15.86236144251702</v>
+        <v>-13.87621921961545</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-16.89583932849727</v>
       </c>
       <c r="E56">
-        <v>-27.43722144756997</v>
+        <v>-23.83007434772989</v>
       </c>
       <c r="F56">
-        <v>-1.918628277446</v>
+        <v>-0.2516117756434408</v>
       </c>
       <c r="G56">
-        <v>-15.76062333654593</v>
+        <v>-13.99152275448197</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-16.90517344461576</v>
       </c>
       <c r="E57">
-        <v>-28.13462869323518</v>
+        <v>-22.42459856292864</v>
       </c>
       <c r="F57">
-        <v>-1.544679209167621</v>
+        <v>-0.1040969369203076</v>
       </c>
       <c r="G57">
-        <v>-14.73279538235365</v>
+        <v>-14.35410165792348</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-16.90112088358669</v>
       </c>
       <c r="E58">
-        <v>-26.30076577312316</v>
+        <v>-22.38918828317315</v>
       </c>
       <c r="F58">
-        <v>-0.9861135545621232</v>
+        <v>-0.4768191930751396</v>
       </c>
       <c r="G58">
-        <v>-16.53305520111254</v>
+        <v>-13.32669011749349</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-16.87395533252676</v>
       </c>
       <c r="E59">
-        <v>-25.50503955576529</v>
+        <v>-21.76916782412347</v>
       </c>
       <c r="F59">
-        <v>-0.7461777647086493</v>
+        <v>-0.2436735308224131</v>
       </c>
       <c r="G59">
-        <v>-16.13159447847558</v>
+        <v>-14.4368257110375</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.84012809724839</v>
       </c>
       <c r="E60">
-        <v>-26.07307426866209</v>
+        <v>-22.39828381597452</v>
       </c>
       <c r="F60">
-        <v>-1.221277119808069</v>
+        <v>-0.1262690188236392</v>
       </c>
       <c r="G60">
-        <v>-15.07688368722861</v>
+        <v>-14.41376108794731</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.79796744729336</v>
       </c>
       <c r="E61">
-        <v>-24.87712799519844</v>
+        <v>-21.60441408407884</v>
       </c>
       <c r="F61">
-        <v>-1.792089358096555</v>
+        <v>-0.3495388849001899</v>
       </c>
       <c r="G61">
-        <v>-15.08891660904905</v>
+        <v>-13.82947383771157</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.74791630368006</v>
       </c>
       <c r="E62">
-        <v>-24.86076434257861</v>
+        <v>-21.63582897453985</v>
       </c>
       <c r="F62">
-        <v>-1.831889926698863</v>
+        <v>-0.3363347084995658</v>
       </c>
       <c r="G62">
-        <v>-16.05275651868543</v>
+        <v>-13.97344856967769</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.69678261007326</v>
       </c>
       <c r="E63">
-        <v>-25.73614499993537</v>
+        <v>-21.47120813725762</v>
       </c>
       <c r="F63">
-        <v>-1.643917624023002</v>
+        <v>-0.5873863605312064</v>
       </c>
       <c r="G63">
-        <v>-15.96158670681917</v>
+        <v>-14.39086877400013</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.62629578073254</v>
       </c>
       <c r="E64">
-        <v>-22.80509917166412</v>
+        <v>-21.34389559730633</v>
       </c>
       <c r="F64">
-        <v>-1.489099069909386</v>
+        <v>-0.4673840883572532</v>
       </c>
       <c r="G64">
-        <v>-15.74263139019627</v>
+        <v>-13.9569656337017</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.54430688632075</v>
       </c>
       <c r="E65">
-        <v>-25.62073971685236</v>
+        <v>-21.1620804651393</v>
       </c>
       <c r="F65">
-        <v>-1.318173740015736</v>
+        <v>-0.4160120555052391</v>
       </c>
       <c r="G65">
-        <v>-15.1319403745383</v>
+        <v>-14.31387269451902</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-16.42965826519825</v>
       </c>
       <c r="E66">
-        <v>-25.31595630377982</v>
+        <v>-20.61200839122239</v>
       </c>
       <c r="F66">
-        <v>-1.604923885271021</v>
+        <v>-0.3195031112420827</v>
       </c>
       <c r="G66">
-        <v>-16.01224037337595</v>
+        <v>-14.28148640786626</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.29562652380735</v>
       </c>
       <c r="E67">
-        <v>-24.98116593888539</v>
+        <v>-20.66158527480687</v>
       </c>
       <c r="F67">
-        <v>-0.7543819154659755</v>
+        <v>-0.7096136275490791</v>
       </c>
       <c r="G67">
-        <v>-15.77192786062545</v>
+        <v>-14.45518185625762</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.13282188313846</v>
       </c>
       <c r="E68">
-        <v>-24.08855360774191</v>
+        <v>-20.69232734503325</v>
       </c>
       <c r="F68">
-        <v>-1.816556017705642</v>
+        <v>-0.7015271049629502</v>
       </c>
       <c r="G68">
-        <v>-16.33804563387934</v>
+        <v>-14.52321655492973</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.95008610430182</v>
       </c>
       <c r="E69">
-        <v>-22.97922255645756</v>
+        <v>-20.38658038693335</v>
       </c>
       <c r="F69">
-        <v>-1.023182995837401</v>
+        <v>-0.6958544449885793</v>
       </c>
       <c r="G69">
-        <v>-15.37927056874971</v>
+        <v>-14.23321765649346</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.75390117856038</v>
       </c>
       <c r="E70">
-        <v>-21.96786160711459</v>
+        <v>-20.72031998936259</v>
       </c>
       <c r="F70">
-        <v>-2.386162153055652</v>
+        <v>-0.7825828553268819</v>
       </c>
       <c r="G70">
-        <v>-16.12542528900678</v>
+        <v>-14.62531885977129</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.53966560230176</v>
       </c>
       <c r="E71">
-        <v>-22.63510823213889</v>
+        <v>-20.83685909913728</v>
       </c>
       <c r="F71">
-        <v>-0.8821020867318117</v>
+        <v>-0.5240261946258779</v>
       </c>
       <c r="G71">
-        <v>-15.24531717989658</v>
+        <v>-13.91995310763348</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.32621629160205</v>
       </c>
       <c r="E72">
-        <v>-23.38337155047663</v>
+        <v>-20.77809946531361</v>
       </c>
       <c r="F72">
-        <v>-1.901816561006183</v>
+        <v>-0.8261235027528295</v>
       </c>
       <c r="G72">
-        <v>-15.48591034769062</v>
+        <v>-13.92753601529837</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.10397721029278</v>
       </c>
       <c r="E73">
-        <v>-24.59732614824474</v>
+        <v>-20.93610423695538</v>
       </c>
       <c r="F73">
-        <v>-1.825673029340853</v>
+        <v>-0.687492904424721</v>
       </c>
       <c r="G73">
-        <v>-16.34577213249674</v>
+        <v>-14.3390546314726</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.89381347631913</v>
       </c>
       <c r="E74">
-        <v>-24.70640193726871</v>
+        <v>-21.28523564055445</v>
       </c>
       <c r="F74">
-        <v>-1.875792570679834</v>
+        <v>-1.028959201737122</v>
       </c>
       <c r="G74">
-        <v>-15.58652583348754</v>
+        <v>-14.5224633551152</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.6866521386847</v>
       </c>
       <c r="E75">
-        <v>-23.15444238904075</v>
+        <v>-21.01267284093992</v>
       </c>
       <c r="F75">
-        <v>-1.207370487849871</v>
+        <v>-0.830918093280233</v>
       </c>
       <c r="G75">
-        <v>-15.42057254818112</v>
+        <v>-13.8923327352318</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.4985667709711</v>
       </c>
       <c r="E76">
-        <v>-24.65971984197764</v>
+        <v>-21.17194018882445</v>
       </c>
       <c r="F76">
-        <v>-1.94332687992787</v>
+        <v>-0.9480161093399712</v>
       </c>
       <c r="G76">
-        <v>-16.44119615267422</v>
+        <v>-13.44015046667868</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.32996104338286</v>
       </c>
       <c r="E77">
-        <v>-25.83472147073018</v>
+        <v>-21.10281829274533</v>
       </c>
       <c r="F77">
-        <v>-2.097512561345747</v>
+        <v>-0.6610969771345148</v>
       </c>
       <c r="G77">
-        <v>-15.16760967251438</v>
+        <v>-13.92871607185356</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.17756304245766</v>
       </c>
       <c r="E78">
-        <v>-25.55648123123462</v>
+        <v>-22.04194243751556</v>
       </c>
       <c r="F78">
-        <v>-1.939828684385847</v>
+        <v>-0.888670211868609</v>
       </c>
       <c r="G78">
-        <v>-15.28910067206184</v>
+        <v>-13.53838234266391</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.04943997982255</v>
       </c>
       <c r="E79">
-        <v>-26.66651002202154</v>
+        <v>-21.78401970782106</v>
       </c>
       <c r="F79">
-        <v>-2.004342766083275</v>
+        <v>-1.375379964485667</v>
       </c>
       <c r="G79">
-        <v>-14.78641485476593</v>
+        <v>-12.99177335836711</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.93021391222278</v>
       </c>
       <c r="E80">
-        <v>-26.13319615580031</v>
+        <v>-22.84431379299316</v>
       </c>
       <c r="F80">
-        <v>-2.445599170941322</v>
+        <v>-1.156528610135649</v>
       </c>
       <c r="G80">
-        <v>-15.03284042597653</v>
+        <v>-13.38363567851485</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.83111230898849</v>
       </c>
       <c r="E81">
-        <v>-25.90587844035847</v>
+        <v>-23.3470184917504</v>
       </c>
       <c r="F81">
-        <v>-2.291213024611967</v>
+        <v>-0.891116380809076</v>
       </c>
       <c r="G81">
-        <v>-15.44104339652004</v>
+        <v>-12.96329535636725</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.73463890941309</v>
       </c>
       <c r="E82">
-        <v>-26.033398640876</v>
+        <v>-23.90717871597533</v>
       </c>
       <c r="F82">
-        <v>-1.981649641083583</v>
+        <v>-1.305444218136916</v>
       </c>
       <c r="G82">
-        <v>-14.71094345012603</v>
+        <v>-12.88238968686094</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.6496522702658</v>
       </c>
       <c r="E83">
-        <v>-26.71959221596417</v>
+        <v>-24.12537597934785</v>
       </c>
       <c r="F83">
-        <v>-1.686970363048701</v>
+        <v>-1.292336132355016</v>
       </c>
       <c r="G83">
-        <v>-16.18919272564472</v>
+        <v>-12.78426615677625</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.56525491575741</v>
       </c>
       <c r="E84">
-        <v>-27.45686613713641</v>
+        <v>-25.13061509519802</v>
       </c>
       <c r="F84">
-        <v>-1.420643616109438</v>
+        <v>-1.29546487603539</v>
       </c>
       <c r="G84">
-        <v>-15.53505630924603</v>
+        <v>-12.77035219347791</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.47835360168629</v>
       </c>
       <c r="E85">
-        <v>-29.09369655878724</v>
+        <v>-25.94123057515541</v>
       </c>
       <c r="F85">
-        <v>-1.96398056438187</v>
+        <v>-1.356804653845291</v>
       </c>
       <c r="G85">
-        <v>-14.71516241338527</v>
+        <v>-12.14868169144201</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.38827635713988</v>
       </c>
       <c r="E86">
-        <v>-29.55151127294008</v>
+        <v>-27.42684257246923</v>
       </c>
       <c r="F86">
-        <v>-1.891379960098313</v>
+        <v>-1.394010775742031</v>
       </c>
       <c r="G86">
-        <v>-14.0917505447071</v>
+        <v>-12.43947556160628</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.2815431831334</v>
       </c>
       <c r="E87">
-        <v>-28.53679245224098</v>
+        <v>-27.16676017288581</v>
       </c>
       <c r="F87">
-        <v>-2.382716144660006</v>
+        <v>-1.224152383063186</v>
       </c>
       <c r="G87">
-        <v>-15.19603154350554</v>
+        <v>-12.45023182932167</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.16799699128777</v>
       </c>
       <c r="E88">
-        <v>-32.13910521409896</v>
+        <v>-28.83035804152516</v>
       </c>
       <c r="F88">
-        <v>-1.761428167049335</v>
+        <v>-1.31517753511981</v>
       </c>
       <c r="G88">
-        <v>-14.12775401799085</v>
+        <v>-12.04240480599927</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.0341171663896</v>
       </c>
       <c r="E89">
-        <v>-31.79240136251926</v>
+        <v>-29.09616771952551</v>
       </c>
       <c r="F89">
-        <v>-1.266682422257719</v>
+        <v>-1.642159828394262</v>
       </c>
       <c r="G89">
-        <v>-15.09355851293205</v>
+        <v>-11.94010538994109</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.89396890514994</v>
       </c>
       <c r="E90">
-        <v>-31.71982399461789</v>
+        <v>-30.61249686779776</v>
       </c>
       <c r="F90">
-        <v>-2.038628892885147</v>
+        <v>-1.525329375005628</v>
       </c>
       <c r="G90">
-        <v>-14.80488848349265</v>
+        <v>-12.12379215788264</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.74025494592369</v>
       </c>
       <c r="E91">
-        <v>-34.55943479896737</v>
+        <v>-31.75530280236023</v>
       </c>
       <c r="F91">
-        <v>-1.976268566434997</v>
+        <v>-1.603720267434753</v>
       </c>
       <c r="G91">
-        <v>-15.43199716651184</v>
+        <v>-12.43168118362951</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.58370130763321</v>
       </c>
       <c r="E92">
-        <v>-33.50621778589277</v>
+        <v>-32.76345124274345</v>
       </c>
       <c r="F92">
-        <v>-2.2521347923849</v>
+        <v>-1.569234504088807</v>
       </c>
       <c r="G92">
-        <v>-14.61666554682404</v>
+        <v>-11.92767955105968</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.42803335301592</v>
       </c>
       <c r="E93">
-        <v>-35.89976538753302</v>
+        <v>-34.62062613802173</v>
       </c>
       <c r="F93">
-        <v>-2.097488538691066</v>
+        <v>-1.734966798734307</v>
       </c>
       <c r="G93">
-        <v>-15.3018058606145</v>
+        <v>-11.96160226090431</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.26972608596722</v>
       </c>
       <c r="E94">
-        <v>-38.14865248551817</v>
+        <v>-36.27516792936729</v>
       </c>
       <c r="F94">
-        <v>-2.191449424823211</v>
+        <v>-1.497049740241456</v>
       </c>
       <c r="G94">
-        <v>-15.22908487540133</v>
+        <v>-12.56301860640235</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.12376828285499</v>
       </c>
       <c r="E95">
-        <v>-40.05290195455772</v>
+        <v>-38.66662023589416</v>
       </c>
       <c r="F95">
-        <v>-2.085425024204097</v>
+        <v>-1.837442473399828</v>
       </c>
       <c r="G95">
-        <v>-15.18524394685506</v>
+        <v>-12.81291777329142</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.98472618743713</v>
       </c>
       <c r="E96">
-        <v>-42.00363001153342</v>
+        <v>-39.37913271114777</v>
       </c>
       <c r="F96">
-        <v>-2.736897881605379</v>
+        <v>-2.028621386291926</v>
       </c>
       <c r="G96">
-        <v>-15.4696414927711</v>
+        <v>-12.810985822294</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.87071886852445</v>
       </c>
       <c r="E97">
-        <v>-44.08781113140418</v>
+        <v>-41.67077504311636</v>
       </c>
       <c r="F97">
-        <v>-2.458066928720857</v>
+        <v>-2.202368963926914</v>
       </c>
       <c r="G97">
-        <v>-15.02273684440892</v>
+        <v>-13.3266287649956</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.77699428828078</v>
       </c>
       <c r="E98">
-        <v>-46.00622824257555</v>
+        <v>-43.94953411355534</v>
       </c>
       <c r="F98">
-        <v>-3.497479979833801</v>
+        <v>-2.194104342349184</v>
       </c>
       <c r="G98">
-        <v>-14.47088809571776</v>
+        <v>-13.41449337420952</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.71239065527928</v>
       </c>
       <c r="E99">
-        <v>-45.93685092399996</v>
+        <v>-44.8178646946882</v>
       </c>
       <c r="F99">
-        <v>-3.079986122292461</v>
+        <v>-2.281434975789321</v>
       </c>
       <c r="G99">
-        <v>-14.99536449274339</v>
+        <v>-13.12784667182823</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.67778122578824</v>
       </c>
       <c r="E100">
-        <v>-48.6729834298885</v>
+        <v>-47.98161287688393</v>
       </c>
       <c r="F100">
-        <v>-2.936295027500651</v>
+        <v>-2.243443561594728</v>
       </c>
       <c r="G100">
-        <v>-15.10828441779822</v>
+        <v>-13.17549537136064</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.66077187572402</v>
       </c>
       <c r="E101">
-        <v>-50.08299036824514</v>
+        <v>-48.67411829488301</v>
       </c>
       <c r="F101">
-        <v>-3.414626672205795</v>
+        <v>-2.342002715179813</v>
       </c>
       <c r="G101">
-        <v>-16.00877069381436</v>
+        <v>-13.16298598865232</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.67836409690487</v>
       </c>
       <c r="E102">
-        <v>-51.03930050147751</v>
+        <v>-51.00408542265429</v>
       </c>
       <c r="F102">
-        <v>-2.75626759658504</v>
+        <v>-2.656429443730032</v>
       </c>
       <c r="G102">
-        <v>-15.75714843549515</v>
+        <v>-13.92810907373612</v>
       </c>
     </row>
   </sheetData>
